--- a/output/2026-09-02_00_Italia_Marche_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-02_00_Italia_Marche_Utensilerie_e_Macchine_Utensili.xlsx
@@ -536,7 +536,6 @@
           <t>+39 0731 4925</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Utensileria professionale, elettroutensili, compressori dal 1967. Alcune fonti citano anche email info@utensileriafioretti.it (dominio diverso) - non riportata per ambiguita, verificare prima di contatto.</t>
@@ -749,7 +748,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dal 1996, vendita utensili pneumatici/elettrici e articoli tecnici industriali (Festo, Omron). Confermato.</t>
+          <t>Dal 1996, vendita utensili pneumatici/elettrici e articoli tecnici industriali (Festo, Omron). Confermato. [DUPLICATO — vedi anche: 2026-09-01_22_Italia_Marche_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -868,7 +867,6 @@
           <t>+39 0733 814286</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Rivenditore autorizzato AEG e centro assistenza Makita/Kango/Lavor/Karcher; vendita elettroutensili, compressori, generatori.</t>
@@ -928,7 +926,6 @@
           <t>F.lli Carnevali &amp; C. S.a.s.</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Marche - FM (Porto Sant'Elpidio, Via del Commercio 13)</t>
@@ -944,7 +941,6 @@
           <t>+39 0734 991158</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>20.000+ referenze, macchinari/materiali di consumo per hobbisti e industria (calzaturiero, carpenteria, modellismo), compressori, aria compressa. Verificare peso reale della componente utensileria/macchine utensili.</t>
@@ -977,8 +973,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Dal 1986, ingrosso viteria/bulloneria/sistemi di fissaggio, abrasivi, utensileria, 40.000+ articoli.</t>

--- a/output/2026-09-02_00_Italia_Marche_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-02_00_Italia_Marche_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
